--- a/branches/release/2027.0.0-ballot/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
+++ b/branches/release/2027.0.0-ballot/ValueSet-mii-vs-mikrobio-resistenzmechanismen-determinanten-loinc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:59:48+00:00</t>
+    <t>2026-09-14T15:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
